--- a/E_sample.xlsx
+++ b/E_sample.xlsx
@@ -112,7 +112,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Chapter 01/관계대명사</t>
+    <t>Chapter 09/관계사</t>
   </si>
   <si>
     <t>2</t>
@@ -154,13 +154,13 @@
     <t>14</t>
   </si>
   <si>
-    <t>GR-E-CH01-C2</t>
-  </si>
-  <si>
-    <t>GR-E-CH01-C1</t>
-  </si>
-  <si>
-    <t>GR-E-CH01-C3</t>
+    <t>GR-E-CH09-C2</t>
+  </si>
+  <si>
+    <t>GR-E-CH09-C1</t>
+  </si>
+  <si>
+    <t>GR-E-CH09-C3</t>
   </si>
   <si>
     <t>관계대명사 that</t>
